--- a/prep_and_checklists/Urby  /PREPLIST_Urby  _12-31-2025_0.xlsx
+++ b/prep_and_checklists/Urby  /PREPLIST_Urby  _12-31-2025_0.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Urby  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938ECD80-FE21-4745-A21D-0F619354315B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C6D5DC-3C91-D845-BBA1-253DFBF1BB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="280" yWindow="760" windowWidth="30240" windowHeight="18020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prep_sheet" sheetId="1" r:id="rId1"/>
     <sheet name="order_sheet" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -786,27 +799,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -840,6 +839,28 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="3">
@@ -909,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -917,31 +938,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,6 +1275,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1254,732 +1288,735 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="D4" s="11" t="s">
+      <c r="B4" s="7"/>
+      <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="19" x14ac:dyDescent="0.2">
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="D5" s="12" t="s">
+      <c r="B5" s="7"/>
+      <c r="D5" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="13" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="13" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="13" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="13" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="11" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="13" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="13" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="13" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="13" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="13" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="13" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="D19" s="3" t="s">
+    <row r="19" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="13" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="13" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="13" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="13" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="13" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="E29" s="15"/>
+    </row>
+    <row r="30" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="D31" s="3" t="s">
+      <c r="E30" s="17"/>
+    </row>
+    <row r="31" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="13" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="13" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="13" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="13" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="D37" s="3" t="s">
+    <row r="37" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="13" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="13" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="13" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="13" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
+    <row r="43" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="13" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="D44" s="4" t="s">
+    <row r="44" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D44" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="13" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="13" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="13" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="13" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
+    <row r="48" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="13" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+    <row r="49" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
+    <row r="51" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="13" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
+    <row r="52" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="13" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
+    <row r="53" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="D54" s="3" t="s">
+    <row r="54" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D54" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
+    <row r="55" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="13" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
+    <row r="56" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="13" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
+    <row r="57" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="13" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
+    <row r="58" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
+    <row r="59" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
+    <row r="60" spans="1:5" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="13" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="2" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="2" t="s">
         <v>222</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D29:E29"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="47" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -1989,14 +2026,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -2010,843 +2047,844 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8" t="s">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8" t="s">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8" t="s">
+      <c r="B30" s="5"/>
+      <c r="C30" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8" t="s">
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8" t="s">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8" t="s">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8" t="s">
+      <c r="B35" s="5"/>
+      <c r="C35" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8" t="s">
+      <c r="B36" s="5"/>
+      <c r="C36" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8" t="s">
+      <c r="B37" s="5"/>
+      <c r="C37" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8" t="s">
+      <c r="B38" s="5"/>
+      <c r="C38" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8" t="s">
+      <c r="B39" s="5"/>
+      <c r="C39" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="5"/>
+      <c r="C40" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8" t="s">
+      <c r="B44" s="5"/>
+      <c r="C44" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8" t="s">
+      <c r="B47" s="5"/>
+      <c r="C47" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8" t="s">
+      <c r="B48" s="5"/>
+      <c r="C48" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8" t="s">
+      <c r="B49" s="5"/>
+      <c r="C49" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8" t="s">
+      <c r="B51" s="5"/>
+      <c r="C51" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8" t="s">
+      <c r="B53" s="5"/>
+      <c r="C53" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8" t="s">
+      <c r="B54" s="5"/>
+      <c r="C54" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8" t="s">
+      <c r="B57" s="5"/>
+      <c r="C57" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8" t="s">
+      <c r="B58" s="5"/>
+      <c r="C58" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8" t="s">
+      <c r="B59" s="5"/>
+      <c r="C59" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8" t="s">
+      <c r="B60" s="5"/>
+      <c r="C60" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8" t="s">
+      <c r="B62" s="5"/>
+      <c r="C62" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8" t="s">
+      <c r="B63" s="5"/>
+      <c r="C63" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8" t="s">
+      <c r="B64" s="5"/>
+      <c r="C64" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8" t="s">
+      <c r="B65" s="5"/>
+      <c r="C65" s="5" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8" t="s">
+      <c r="B66" s="5"/>
+      <c r="C66" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8" t="s">
+      <c r="B67" s="5"/>
+      <c r="C67" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8" t="s">
+      <c r="B68" s="5"/>
+      <c r="C68" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8" t="s">
+      <c r="B69" s="5"/>
+      <c r="C69" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8" t="s">
+      <c r="B70" s="5"/>
+      <c r="C70" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8" t="s">
+      <c r="B71" s="5"/>
+      <c r="C71" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8" t="s">
+      <c r="B72" s="5"/>
+      <c r="C72" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8" t="s">
+      <c r="B73" s="5"/>
+      <c r="C73" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8" t="s">
+      <c r="B74" s="5"/>
+      <c r="C74" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8" t="s">
+      <c r="B75" s="5"/>
+      <c r="C75" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8" t="s">
+      <c r="B76" s="5"/>
+      <c r="C76" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8" t="s">
+      <c r="B77" s="5"/>
+      <c r="C77" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8" t="s">
+      <c r="B78" s="5"/>
+      <c r="C78" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8" t="s">
+      <c r="B79" s="5"/>
+      <c r="C79" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8" t="s">
+      <c r="B80" s="5"/>
+      <c r="C80" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8" t="s">
+      <c r="B81" s="5"/>
+      <c r="C81" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8" t="s">
+      <c r="B82" s="5"/>
+      <c r="C82" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8" t="s">
+      <c r="B83" s="5"/>
+      <c r="C83" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A84" s="8" t="s">
+      <c r="A84" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8" t="s">
+      <c r="B84" s="5"/>
+      <c r="C84" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8" t="s">
+      <c r="B85" s="5"/>
+      <c r="C85" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8" t="s">
+      <c r="B86" s="5"/>
+      <c r="C86" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8" t="s">
+      <c r="B87" s="5"/>
+      <c r="C87" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8" t="s">
+      <c r="B88" s="5"/>
+      <c r="C88" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8" t="s">
+      <c r="B89" s="5"/>
+      <c r="C89" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8" t="s">
+      <c r="B90" s="5"/>
+      <c r="C90" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8" t="s">
+      <c r="B91" s="5"/>
+      <c r="C91" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8" t="s">
+      <c r="B92" s="5"/>
+      <c r="C92" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8" t="s">
+      <c r="B93" s="5"/>
+      <c r="C93" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8" t="s">
+      <c r="B94" s="5"/>
+      <c r="C94" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8" t="s">
+      <c r="B95" s="5"/>
+      <c r="C95" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8" t="s">
+      <c r="B96" s="5"/>
+      <c r="C96" s="5" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>